--- a/eval_results_v2.xlsx
+++ b/eval_results_v2.xlsx
@@ -413,802 +413,802 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>96 + 665</v>
+        <v>467 + 24</v>
       </c>
       <c r="B2" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317253862.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [467+24]: Upload failed (409): {"message":"is at 01d9e95f50bb83ce262203cd69464f35c5e70765 but expected 713d48b331519a2492f44a0d22020b67f2d781f0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>403 + 376</v>
+        <v>520 + 331</v>
       </c>
       <c r="B3" t="str">
-        <v>❌ 渲染失败 [403+376]: Upload failed (409): {"message":"is at 341fe5273afb4407215a93aa73c9f8d159da503c but expected 74b252dd14f31d0d49c5c2780e8e4595b4886bfe","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319972780_prgwk.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>446 + 876</v>
+        <v>553 + 34</v>
       </c>
       <c r="B4" t="str">
-        <v>❌ 渲染失败 [446+876]: Upload failed (409): {"message":"is at 341fe5273afb4407215a93aa73c9f8d159da503c but expected 74b252dd14f31d0d49c5c2780e8e4595b4886bfe","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319969778_zzuwd.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>99 + 48</v>
+        <v>276 + 426</v>
       </c>
       <c r="B5" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317255687.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319973747_z7t69.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>39 + 463</v>
+        <v>231 + 121</v>
       </c>
       <c r="B6" t="str">
-        <v>❌ 渲染失败 [39+463]: Upload failed (409): {"message":"is at 9b960befd745ee14d38022023df26fd416ea60e6 but expected 341fe5273afb4407215a93aa73c9f8d159da503c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [231+121]: Upload failed (409): {"message":"is at 047e818b175243205e5ec92530dd375e138c19da but expected 8a6c5a4c0b48b5350f23e5c2864fbfb02fc83557","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>169 + 881（含验算）</v>
+        <v>299 + 690（含验算）</v>
       </c>
       <c r="B7" t="str">
-        <v>❌ 渲染失败 [169+881]: Upload failed (409): {"message":"is at 9b960befd745ee14d38022023df26fd416ea60e6 but expected 341fe5273afb4407215a93aa73c9f8d159da503c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319974013_na04b.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>728 + 29（含验算）</v>
+        <v>83 + 245（含验算）</v>
       </c>
       <c r="B8" t="str">
-        <v>❌ 渲染失败 [728+29]: Upload failed (409): {"message":"is at 4ffac2d1339696fa8abb710fa5816d7b22ea0b8f but expected 9b960befd745ee14d38022023df26fd416ea60e6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [83+245]: Upload failed (409): {"message":"is at 4d3bcf996e3be3582d17cf08e07da3894b239631 but expected 047e818b175243205e5ec92530dd375e138c19da","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>424 + 340（含验算）</v>
+        <v>143 + 734（含验算）</v>
       </c>
       <c r="B9" t="str">
-        <v>❌ 渲染失败 [424+340]: Upload failed (409): {"message":"is at 4ffac2d1339696fa8abb710fa5816d7b22ea0b8f but expected 9b960befd745ee14d38022023df26fd416ea60e6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319975554_9v3r6.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>211 + 183（含验算）</v>
+        <v>155 + 524（含验算）</v>
       </c>
       <c r="B10" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317256883.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319975912_vgz3m.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>844 + 391（含验算）</v>
+        <v>582 + 56（含验算）</v>
       </c>
       <c r="B11" t="str">
-        <v>❌ 渲染失败 [844+391]: Upload failed (409): {"message":"is at 7308d7ad8e0fd1c95aef49a9e24c2792c956371b but expected 4ffac2d1339696fa8abb710fa5816d7b22ea0b8f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319977313_n49ng.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>332.8 + 755.5</v>
+        <v>456.7 + 23.9</v>
       </c>
       <c r="B12" t="str">
-        <v>❌ 渲染失败 [332.8+755.5]: Upload failed (409): {"message":"is at 7308d7ad8e0fd1c95aef49a9e24c2792c956371b but expected 4ffac2d1339696fa8abb710fa5816d7b22ea0b8f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [456.7+23.9]: Upload failed (409): {"message":"is at 2029bbb8707d498562677bdd1825284026768208 but expected 2f51808f52d56b45447b6b24021206aa645c9075","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>450.08 + 308.04</v>
+        <v>587.09 + 720.23</v>
       </c>
       <c r="B13" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317258325.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [587.09+720.23]: Upload failed (409): {"message":"is at 2029bbb8707d498562677bdd1825284026768208 but expected 2f51808f52d56b45447b6b24021206aa645c9075","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>459.1 + 788.9</v>
+        <v>427.5 + 676.2</v>
       </c>
       <c r="B14" t="str">
-        <v>❌ 渲染失败 [459.1+788.9]: Upload failed (409): {"message":"is at b701908b26becec7533f432c5f9ad8a363263479 but expected 7308d7ad8e0fd1c95aef49a9e24c2792c956371b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319980926_n18cb.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>821.5 + 436.63</v>
+        <v>146.9 + 959.21</v>
       </c>
       <c r="B15" t="str">
-        <v>❌ 渲染失败 [821.5+436.63]: Upload failed (409): {"message":"is at b701908b26becec7533f432c5f9ad8a363263479 but expected 7308d7ad8e0fd1c95aef49a9e24c2792c956371b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [146.9+959.21]: Upload failed (409): {"message":"is at 9ef9b444c62e4f5f48761a062087c7f211b58799 but expected 2029bbb8707d498562677bdd1825284026768208","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>659.3 + 337.6</v>
+        <v>146.3 + 716.6</v>
       </c>
       <c r="B16" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317259520.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [146.3+716.6]: Upload failed (409): {"message":"is at 9ef9b444c62e4f5f48761a062087c7f211b58799 but expected 2029bbb8707d498562677bdd1825284026768208","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>219.1 + 761（含验算）</v>
+        <v>665.65 + 5.11（含验算）</v>
       </c>
       <c r="B17" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317261302.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319982429_4gpx9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>780.7 + 270（含验算）</v>
+        <v>47.8 + 705.4（含验算）</v>
       </c>
       <c r="B18" t="str">
-        <v>❌ 渲染失败 [780.7+270]: Upload failed (409): {"message":"is at 7d024b41b9534a8cc90e4d114d234fcb9ca177cd but expected b701908b26becec7533f432c5f9ad8a363263479","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319982718_zbgq9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>549.81 + 490.91（含验算）</v>
+        <v>843.13 + 272.92（含验算）</v>
       </c>
       <c r="B19" t="str">
-        <v>❌ 渲染失败 [549.81+490.91]: Upload failed (409): {"message":"is at 7d024b41b9534a8cc90e4d114d234fcb9ca177cd but expected b701908b26becec7533f432c5f9ad8a363263479","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [843.13+272.92]: Upload failed (409): {"message":"is at d34908ed49ca4cfb65db3488f3948f66896a5fa8 but expected 9ef9b444c62e4f5f48761a062087c7f211b58799","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>475.4 + 21（含验算）</v>
+        <v>598.8 + 445.6（含验算）</v>
       </c>
       <c r="B20" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317262816.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319985246_utuuf.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>392.52 + 39.21（含验算）</v>
+        <v>651.93 + 764.07（含验算）</v>
       </c>
       <c r="B21" t="str">
-        <v>❌ 渲染失败 [392.52+39.21]: Upload failed (409): {"message":"is at d20cb79f9b3495091c9e0d33745f033f60f5cbef but expected 7d024b41b9534a8cc90e4d114d234fcb9ca177cd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [651.93+764.07]: Upload failed (409): {"message":"is at f1347171ffde8e60c267f96908edcfa12a6b0961 but expected 26149f418e999921dc627a594dcc0af50b359182","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>123 - 89</v>
+        <v>95 - 81</v>
       </c>
       <c r="B22" t="str">
-        <v>❌ 渲染失败 [123-89]: Upload failed (409): {"message":"is at d20cb79f9b3495091c9e0d33745f033f60f5cbef but expected 7d024b41b9534a8cc90e4d114d234fcb9ca177cd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319984956_laqws.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>98 - 36</v>
+        <v>14 - 7</v>
       </c>
       <c r="B23" t="str">
-        <v>❌ 渲染失败 [98-36]: Upload failed (409): {"message":"is at 1c93b3b8ab9611c0a8d87fb6be86e01b34d735b6 but expected d20cb79f9b3495091c9e0d33745f033f60f5cbef","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319986508_x7cy9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>423 - 359</v>
+        <v>82 - 59</v>
       </c>
       <c r="B24" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317264080.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [82-59]: Upload failed (409): {"message":"is at e0feef20aec436755752dcbfc76b78f6b21c555b but expected f333bcc16474956805bd4f8251d8673e5b600523","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>16 - 12</v>
+        <v>368 - 152</v>
       </c>
       <c r="B25" t="str">
-        <v>❌ 渲染失败 [16-12]: Upload failed (409): {"message":"is at 1c93b3b8ab9611c0a8d87fb6be86e01b34d735b6 but expected d20cb79f9b3495091c9e0d33745f033f60f5cbef","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [368-152]: Upload failed (409): {"message":"is at e0feef20aec436755752dcbfc76b78f6b21c555b but expected f333bcc16474956805bd4f8251d8673e5b600523","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>540 - 145</v>
+        <v>342 - 287</v>
       </c>
       <c r="B26" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317265581.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [342-287]: Upload failed (409): {"message":"is at ba3bf644244c3b6cebd857f1ea2b1f9def9baab0 but expected e0feef20aec436755752dcbfc76b78f6b21c555b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>129 - 72（含验算）</v>
+        <v>937 - 671（含验算）</v>
       </c>
       <c r="B27" t="str">
-        <v>❌ 渲染失败 [129-72]: Upload failed (409): {"message":"is at 3ff4e6ac32622091d7ef5c9357d53c7c0c339387 but expected 1c93b3b8ab9611c0a8d87fb6be86e01b34d735b6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [937-671]: Upload failed (409): {"message":"is at ba3bf644244c3b6cebd857f1ea2b1f9def9baab0 but expected e0feef20aec436755752dcbfc76b78f6b21c555b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>668 - 224（含验算）</v>
+        <v>775 - 101（含验算）</v>
       </c>
       <c r="B28" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317265855.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319988049_3fhm3.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>678 - 394（含验算）</v>
+        <v>928 - 265（含验算）</v>
       </c>
       <c r="B29" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317268866.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319991347_ht5u7.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>829 - 647（含验算）</v>
+        <v>169 - 109（含验算）</v>
       </c>
       <c r="B30" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317268550.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319991646_u2u8b.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>149 - 108（含验算）</v>
+        <v>612 - 483（含验算）</v>
       </c>
       <c r="B31" t="str">
-        <v>❌ 渲染失败 [149-108]: Upload failed (409): {"message":"is at b370fb840d77b3e7939a0257f19a12b76c12aeab but expected c068e16065045e92c42fe3734d73c84375c9454a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [612-483]: Upload failed (409): {"message":"is at f68bb8ea3ea3872c95080fe26ed7fea9995cf4e3 but expected ba3bf644244c3b6cebd857f1ea2b1f9def9baab0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>950.7 - 120.9</v>
+        <v>913.3 - 218.6</v>
       </c>
       <c r="B32" t="str">
-        <v>❌ 渲染失败 [950.7-120.9]: Upload failed (409): {"message":"is at 0e91b20923532d943852960ce2c54cd06c7bb923 but expected 4faeed9687da7efc5779eb44a33e6338349d6444","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [913.3-218.6]: Upload failed (409): {"message":"is at 9c5a04ef35b68487ceba8bb1b895e6a0376782ee but expected 4b78fa25c0880e7e80be8c2eed9e3bce34833c61","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>584.16 - 149.3</v>
+        <v>562.37 - 141.01</v>
       </c>
       <c r="B33" t="str">
-        <v>❌ 渲染失败 [584.16-149.3]: Upload failed (409): {"message":"is at 0e91b20923532d943852960ce2c54cd06c7bb923 but expected 4faeed9687da7efc5779eb44a33e6338349d6444","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319992844_g71by.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>76.9 - 14.1</v>
+        <v>578.1 - 48.8</v>
       </c>
       <c r="B34" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317270126.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [578.1-48.8]: Upload failed (409): {"message":"is at 9c5a04ef35b68487ceba8bb1b895e6a0376782ee but expected 4b78fa25c0880e7e80be8c2eed9e3bce34833c61","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>223.87 - 182.58</v>
+        <v>942.28 - 821.96</v>
       </c>
       <c r="B35" t="str">
-        <v>❌ 渲染失败 [223.87-182.58]: Upload failed (409): {"message":"is at 8604b16abdd2daa8792e0f4e2757112118648432 but expected 0e91b20923532d943852960ce2c54cd06c7bb923","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319994150_wsghk.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>441.5 - 291</v>
+        <v>123.3 - 69.1</v>
       </c>
       <c r="B36" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317271782.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [123.3-69.1]: Upload failed (409): {"message":"is at 7cbf67ec13cc9cf057d44631e4de29059a33d19f but expected 9c5a04ef35b68487ceba8bb1b895e6a0376782ee","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>670.57 - 526.46（含验算）</v>
+        <v>329.19 - 32.16（含验算）</v>
       </c>
       <c r="B37" t="str">
-        <v>❌ 渲染失败 [670.57-526.46]: Upload failed (409): {"message":"is at 8604b16abdd2daa8792e0f4e2757112118648432 but expected 0e91b20923532d943852960ce2c54cd06c7bb923","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [329.19-32.16]: Upload failed (409): {"message":"is at 7cbf67ec13cc9cf057d44631e4de29059a33d19f but expected 9c5a04ef35b68487ceba8bb1b895e6a0376782ee","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>205.1 - 120.9（含验算）</v>
+        <v>308.3 - 90.3（含验算）</v>
       </c>
       <c r="B38" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317274109.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319995536_8bglr.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>912 - 616.71（含验算）</v>
+        <v>378.97 - 328.42（含验算）</v>
       </c>
       <c r="B39" t="str">
-        <v>❌ 渲染失败 [912-616.71]: Upload failed (409): {"message":"is at 4e340ad0842857e6928c9249311c729b917deac4 but expected 8604b16abdd2daa8792e0f4e2757112118648432","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [378.97-328.42]: Upload failed (409): {"message":"is at 9130d1928488235f60ca790799fb040517fc66a0 but expected 7cbf67ec13cc9cf057d44631e4de29059a33d19f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>119.9 - 42（含验算）</v>
+        <v>995.9 - 830.1（含验算）</v>
       </c>
       <c r="B40" t="str">
-        <v>❌ 渲染失败 [119.9-42]: Upload failed (409): {"message":"is at 4e340ad0842857e6928c9249311c729b917deac4 but expected 8604b16abdd2daa8792e0f4e2757112118648432","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [995.9-830.1]: Upload failed (409): {"message":"is at 9130d1928488235f60ca790799fb040517fc66a0 but expected 7cbf67ec13cc9cf057d44631e4de29059a33d19f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>690.9 - 124.89（含验算）</v>
+        <v>387.4 - 11.63（含验算）</v>
       </c>
       <c r="B41" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317275807.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [387.4-11.63]: Upload failed (409): {"message":"is at 883ca3651c9a68aa4edf142a4aca0924ca286e27 but expected 9130d1928488235f60ca790799fb040517fc66a0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>87 × 2</v>
+        <v>43 × 4</v>
       </c>
       <c r="B42" t="str">
-        <v>❌ 渲染失败 [87×2]: Upload failed (409): {"message":"is at 12dd6dab1002a9cd05184e1b2c70a800b0f258a0 but expected 4e340ad0842857e6928c9249311c729b917deac4","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319997148_zbwxd.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>62 × 7</v>
+        <v>37 × 9</v>
       </c>
       <c r="B43" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317275557.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [37×9]: Upload failed (409): {"message":"is at 883ca3651c9a68aa4edf142a4aca0924ca286e27 but expected 9130d1928488235f60ca790799fb040517fc66a0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>9 × 8</v>
+        <v>61 × 8</v>
       </c>
       <c r="B44" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317277297.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319998731_vypd2.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>67 × 2</v>
+        <v>79 × 2</v>
       </c>
       <c r="B45" t="str">
-        <v>❌ 渲染失败 [67×2]: Upload failed (409): {"message":"is at 9cc41595c8e42ac3d1005457c325ae4db0454ef4 but expected e7f0441d7fe1879397b0bd2e2a475988b7e7db52","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [79×2]: Upload failed (409): {"message":"is at 399b21a0a8449b047393c67fc449a7436c0ae45a but expected 883ca3651c9a68aa4edf142a4aca0924ca286e27","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>53 × 9</v>
+        <v>61 × 4</v>
       </c>
       <c r="B46" t="str">
-        <v>❌ 渲染失败 [53×9]: Upload failed (409): {"message":"is at 9cc41595c8e42ac3d1005457c325ae4db0454ef4 but expected e7f0441d7fe1879397b0bd2e2a475988b7e7db52","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [61×4]: Upload failed (409): {"message":"is at 399b21a0a8449b047393c67fc449a7436c0ae45a but expected 883ca3651c9a68aa4edf142a4aca0924ca286e27","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>36 × 2（含验算）</v>
+        <v>91 × 9（含验算）</v>
       </c>
       <c r="B47" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317278691.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [91×9]: Upload failed (409): {"message":"is at 29717d2e355c9e399812b60f85c87e8814abfa65 but expected 399b21a0a8449b047393c67fc449a7436c0ae45a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>98 × 7（含验算）</v>
+        <v>70 × 4（含验算）</v>
       </c>
       <c r="B48" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317278996.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320000559_0zkrn.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>81 × 1（含验算）</v>
+        <v>36 × 3（含验算）</v>
       </c>
       <c r="B49" t="str">
-        <v>❌ 渲染失败 [81×1]: Upload failed (409): {"message":"is at 04051d53ecf1415c0d983d2bf615282d5d012a90 but expected 9cc41595c8e42ac3d1005457c325ae4db0454ef4","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320000853_islpu.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>66 × 8（含验算）</v>
+        <v>33 × 4（含验算）</v>
       </c>
       <c r="B50" t="str">
-        <v>❌ 渲染失败 [66×8]: Upload failed (409): {"message":"is at 0497ea032e3738f31fcab4b3cf113b2a6a54fc53 but expected 0e523318ca54e7c043384e6e5d04b7d39bcb5fbd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320002536_yxrof.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>20 × 2（含验算）</v>
+        <v>64 × 4（含验算）</v>
       </c>
       <c r="B51" t="str">
-        <v>❌ 渲染失败 [20×2]: Upload failed (409): {"message":"is at 0497ea032e3738f31fcab4b3cf113b2a6a54fc53 but expected 0e523318ca54e7c043384e6e5d04b7d39bcb5fbd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320002318_c3ru9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>25.8 × 7.8</v>
+        <v>86 × 1.8</v>
       </c>
       <c r="B52" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317280059.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [86×1.8]: Upload failed (409): {"message":"is at 5a3313bccb57951d1239b575d017214ea4dc1b85 but expected cd7f4f8df27585b80b682219a702092c89e20ca3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>38.7 × 4.8</v>
+        <v>69 × 6.2</v>
       </c>
       <c r="B53" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317281321.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320004987_lmprd.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>72.6 × 3.6</v>
+        <v>73.2 × 6.9</v>
       </c>
       <c r="B54" t="str">
-        <v>❌ 渲染失败 [72.6×3.6]: Upload failed (409): {"message":"is at 2b858442fc9247ce216d1c5ec5a409a220af9319 but expected 0497ea032e3738f31fcab4b3cf113b2a6a54fc53","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [73.2×6.9]: Upload failed (409): {"message":"is at b113cc0cbb0e1055ca1ea95ffdb564e1fdf0fe7f but expected 208efd60594a9cabe0fdfd7c02c492de38c41116","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>76.5 × 8.2</v>
+        <v>88.8 × 2.6</v>
       </c>
       <c r="B55" t="str">
-        <v>❌ 渲染失败 [76.5×8.2]: Upload failed (409): {"message":"is at 2b858442fc9247ce216d1c5ec5a409a220af9319 but expected 0497ea032e3738f31fcab4b3cf113b2a6a54fc53","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [88.8×2.6]: Upload failed (409): {"message":"is at b113cc0cbb0e1055ca1ea95ffdb564e1fdf0fe7f but expected 208efd60594a9cabe0fdfd7c02c492de38c41116","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>52.7 × 4.3</v>
+        <v>7.9 × 4.2</v>
       </c>
       <c r="B56" t="str">
-        <v>❌ 渲染失败 [52.7×4.3]: Upload failed (409): {"message":"is at 5fd472cc366b1037ca9bcc7cc6ecd4d0985d48af but expected 2b858442fc9247ce216d1c5ec5a409a220af9319","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320006108_myhee.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>86.5 × 4.2（含验算）</v>
+        <v>58.2 × 6（含验算）</v>
       </c>
       <c r="B57" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317282952.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320006371_pgv0q.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>79.1 × 1.3（含验算）</v>
+        <v>97.4 × 3.8（含验算）</v>
       </c>
       <c r="B58" t="str">
-        <v>❌ 渲染失败 [79.1×1.3]: Upload failed (409): {"message":"is at 5fd472cc366b1037ca9bcc7cc6ecd4d0985d48af but expected 2b858442fc9247ce216d1c5ec5a409a220af9319","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [97.4×3.8]: Upload failed (409): {"message":"is at be6015111a40640004d56157626b7104b4fb00a0 but expected 6b93b68bb9cca91a7b289b47883fe3cafcc337ba","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>8 × 8.6（含验算）</v>
+        <v>36.3 × 6.5（含验算）</v>
       </c>
       <c r="B59" t="str">
-        <v>❌ 渲染失败 [8×8.6]: Upload failed (409): {"message":"is at 8dbbfba1716def58c347c3df3d3f54d37c8eeb1e but expected 5fd472cc366b1037ca9bcc7cc6ecd4d0985d48af","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320007871_tapq5.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>90.9 × 1.9（含验算）</v>
+        <v>78.3 × 7.8（含验算）</v>
       </c>
       <c r="B60" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317285327.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320008179_4kcue.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>65.1 × 2.7（含验算）</v>
+        <v>14.9 × 6.8（含验算）</v>
       </c>
       <c r="B61" t="str">
-        <v>❌ 渲染失败 [65.1×2.7]: Upload failed (409): {"message":"is at 8dbbfba1716def58c347c3df3d3f54d37c8eeb1e but expected 5fd472cc366b1037ca9bcc7cc6ecd4d0985d48af","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [14.9×6.8]: Upload failed (409): {"message":"is at 57c3cf0e28e67f88a915ebddc2fdd7d91e6e6b33 but expected be6015111a40640004d56157626b7104b4fb00a0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>54 ÷ 7</v>
+        <v>30 ÷ 7</v>
       </c>
       <c r="B62" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317290353.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [30÷7]: Upload failed (409): {"message":"is at a4179a6564e9ca53da43b6ff45abea5b41fdbe13 but expected 93538a39adc33646990ad398dc2b857bee5b409b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>95 ÷ 8</v>
+        <v>33 ÷ 8</v>
       </c>
       <c r="B63" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317290867.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [33÷8]: Upload failed (409): {"message":"is at a4179a6564e9ca53da43b6ff45abea5b41fdbe13 but expected 93538a39adc33646990ad398dc2b857bee5b409b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>66 ÷ 7</v>
+        <v>22 ÷ 8</v>
       </c>
       <c r="B64" t="str">
-        <v>❌ 渲染失败 [66÷7]: Upload failed (409): {"message":"is at 6a7f4e49b50a19c63686fe714d83b9788f5e76ca but expected 8dbbfba1716def58c347c3df3d3f54d37c8eeb1e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320010261_apgo4.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>67 ÷ 6</v>
+        <v>17 ÷ 7</v>
       </c>
       <c r="B65" t="str">
-        <v>❌ 渲染失败 [67÷6]: Upload failed (409): {"message":"is at 0f9ac58ef2851ef7f00ed989e6b6bbd4ad31895c but expected 61ab42dfc0c5d03c48ef8c33cd35303250ac91c9","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320012085_tnk9h.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>15 ÷ 4</v>
+        <v>27 ÷ 8</v>
       </c>
       <c r="B66" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317292406.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [27÷8]: Upload failed (409): {"message":"is at ace6e6c1dce608c9058f7771e7946b1aab4eadd3 but expected a4179a6564e9ca53da43b6ff45abea5b41fdbe13","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>98 ÷ 6（含验算）</v>
+        <v>30 ÷ 7（含验算）</v>
       </c>
       <c r="B67" t="str">
-        <v>❌ 渲染失败 [98÷6]: Upload failed (409): {"message":"is at 0f9ac58ef2851ef7f00ed989e6b6bbd4ad31895c but expected 61ab42dfc0c5d03c48ef8c33cd35303250ac91c9","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320011932_u9mn2.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>28 ÷ 6（含验算）</v>
+        <v>28 ÷ 8（含验算）</v>
       </c>
       <c r="B68" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317295345.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [28÷8]: Upload failed (409): {"message":"is at ddc02e192b654076d9ad05ace73c5bf839a386b7 but expected cb8558f3910b6ff8cf3fdfe2b66666fcede7d7f6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>69 ÷ 4（含验算）</v>
+        <v>85 ÷ 8（含验算）</v>
       </c>
       <c r="B69" t="str">
-        <v>❌ 渲染失败 [69÷4]: Upload failed (409): {"message":"is at b981ba08dbf666c7a32566c06775bb8506328cc0 but expected 0f9ac58ef2851ef7f00ed989e6b6bbd4ad31895c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [85÷8]: Upload failed (409): {"message":"is at ddc02e192b654076d9ad05ace73c5bf839a386b7 but expected cb8558f3910b6ff8cf3fdfe2b66666fcede7d7f6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>36 ÷ 8（含验算）</v>
+        <v>81 ÷ 5（含验算）</v>
       </c>
       <c r="B70" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317294852.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320013591_eygax.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>42 ÷ 5（含验算）</v>
+        <v>27 ÷ 9（含验算）</v>
       </c>
       <c r="B71" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317296488.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320015605_kam80.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>17.8 ÷ 2.1</v>
+        <v>58.4 ÷ 4.8</v>
       </c>
       <c r="B72" t="str">
-        <v>❌ 渲染失败 [17.8÷2.1]: Upload failed (409): {"message":"is at ecf95c735c9b6b33b0e53734c3f45162c11e600b but expected 2f54f0d179db1215caf7f2e8ffa9b1e71e1e44c6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [58.4÷4.8]: Upload failed (409): {"message":"is at d8a60d3599b5924687a5761cb7c93dfa4069d8bc but expected ddc02e192b654076d9ad05ace73c5bf839a386b7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>34 ÷ 2.7</v>
+        <v>76.6 ÷ 4.5</v>
       </c>
       <c r="B73" t="str">
-        <v>❌ 渲染失败 [34÷2.7]: Upload failed (409): {"message":"is at ecf95c735c9b6b33b0e53734c3f45162c11e600b but expected 2f54f0d179db1215caf7f2e8ffa9b1e71e1e44c6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [76.6÷4.5]: Upload failed (409): {"message":"is at d8a60d3599b5924687a5761cb7c93dfa4069d8bc but expected ddc02e192b654076d9ad05ace73c5bf839a386b7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>37.1 ÷ 8.7</v>
+        <v>93.2 ÷ 7.5</v>
       </c>
       <c r="B74" t="str">
-        <v>❌ 渲染失败 [37.1÷8.7]: Upload failed (409): {"message":"is at 81a093583fcae4983bbc8203149e68f9f549d53d but expected ecf95c735c9b6b33b0e53734c3f45162c11e600b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [93.2÷7.5]: Upload failed (409): {"message":"is at fa81a2c25e2424544e5c582ad87b4b6bcb613d1a but expected d8a60d3599b5924687a5761cb7c93dfa4069d8bc","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>92.7 ÷ 7.8</v>
+        <v>85.3 ÷ 2.2</v>
       </c>
       <c r="B75" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317298290.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320017450_2u4ri.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>36.7 ÷ 7.7</v>
+        <v>87.5 ÷ 6</v>
       </c>
       <c r="B76" t="str">
-        <v>❌ 渲染失败 [36.7÷7.7]: Upload failed (409): {"message":"is at 81a093583fcae4983bbc8203149e68f9f549d53d but expected ecf95c735c9b6b33b0e53734c3f45162c11e600b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320017692_25lyt.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>47.3 ÷ 7.3（含验算）</v>
+        <v>51.2 ÷ 6.8（含验算）</v>
       </c>
       <c r="B77" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317299998.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320019221_8gzj0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>33.2 ÷ 3.3（含验算）</v>
+        <v>15.4 ÷ 6.8（含验算）</v>
       </c>
       <c r="B78" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317299739.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [15.4÷6.8]: Upload failed (409): {"message":"is at 54e43afff8ebcccaa503d04f98d1aafc4f9928f2 but expected 99dfa6849b6acbfd864c577fe057e9f8f11b544d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>74.6 ÷ 8.1（含验算）</v>
+        <v>59 ÷ 8（含验算）</v>
       </c>
       <c r="B79" t="str">
-        <v>❌ 渲染失败 [74.6÷8.1]: Upload failed (409): {"message":"is at 19c9062bbc1b84596f0240b7d79fb7e32c3ec1b4 but expected 50e4f13af5673d363d189d90c92abd83ceb91aa3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [59÷8]: Upload failed (409): {"message":"is at 54e43afff8ebcccaa503d04f98d1aafc4f9928f2 but expected 99dfa6849b6acbfd864c577fe057e9f8f11b544d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>32.2 ÷ 6（含验算）</v>
+        <v>31.9 ÷ 8.6（含验算）</v>
       </c>
       <c r="B80" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317301640.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [31.9÷8.6]: Upload failed (409): {"message":"is at 5c7fa58d66a0cdadbc2644b21d9106afc9269fb3 but expected 04aaf0c0643e930f400233dd15f12d79da04bf40","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>25.2 ÷ 2.9（含验算）</v>
+        <v>23.8 ÷ 6.1（含验算）</v>
       </c>
       <c r="B81" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317301907.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320021498_so46c.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>616 ÷ 7 (整除)</v>
+        <v>366 ÷ 6 (整除)</v>
       </c>
       <c r="B82" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317301420.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320021232_nerb0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>194 ÷ 4 (整除)</v>
+        <v>53 ÷ 2 (整除)</v>
       </c>
       <c r="B83" t="str">
-        <v>❌ 渲染失败 [194÷4(整除)]: Upload failed (409): {"message":"is at 30fd595f50310c327ebc0292df1a809df540d331 but expected 427873675d1f9abfb742b4efc65785abd4db9193","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [53÷2(整除)]: Upload failed (409): {"message":"is at 49ebb53844cfec8a61cb3906d98899bf7eb01373 but expected 5c7fa58d66a0cdadbc2644b21d9106afc9269fb3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>265 ÷ 5 (整除)</v>
+        <v>426 ÷ 6 (整除)</v>
       </c>
       <c r="B84" t="str">
-        <v>❌ 渲染失败 [265÷5(整除)]: Upload failed (409): {"message":"is at 30fd595f50310c327ebc0292df1a809df540d331 but expected 427873675d1f9abfb742b4efc65785abd4db9193","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [426÷6(整除)]: Upload failed (409): {"message":"is at 49ebb53844cfec8a61cb3906d98899bf7eb01373 but expected 5c7fa58d66a0cdadbc2644b21d9106afc9269fb3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>534 ÷ 9 (整除)</v>
+        <v>297 ÷ 4 (整除)</v>
       </c>
       <c r="B85" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317303987.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320023165_wlecr.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>539 ÷ 7 (整除)</v>
+        <v>612 ÷ 9 (整除)</v>
       </c>
       <c r="B86" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317305403.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [612÷9(整除)]: Upload failed (409): {"message":"is at 2c7a933b4064185cf6f6f644c765874141ffb610 but expected 49ebb53844cfec8a61cb3906d98899bf7eb01373","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>54 ÷ 4 (整除)（含验算）</v>
+        <v>118 ÷ 8 (整除)（含验算）</v>
       </c>
       <c r="B87" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317305774.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320024881_6soaz.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>420 ÷ 6 (整除)（含验算）</v>
+        <v>172 ÷ 2 (整除)（含验算）</v>
       </c>
       <c r="B88" t="str">
-        <v>❌ 渲染失败 [420÷6(整除)]: Upload failed (409): {"message":"is at 95c52a1dc70409dab81958d0fb6a5997c17aca7c but expected 272181bf96838b8992b31583bc187e7b2594d495","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320024542_4gqss.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>193 ÷ 5 (整除)（含验算）</v>
+        <v>271 ÷ 8 (整除)（含验算）</v>
       </c>
       <c r="B89" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317307687.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320026333_xa3ey.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>252 ÷ 6 (整除)（含验算）</v>
+        <v>686 ÷ 7 (整除)（含验算）</v>
       </c>
       <c r="B90" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317307296.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [686÷7(整除)]: Upload failed (409): {"message":"is at d98085b09cdb5b7284fd3055bd65989528bae116 but expected 209cf934640c19226ef1ab1f2ed014de0fd53298","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>95 ÷ 2 (整除)（含验算）</v>
+        <v>221 ÷ 9 (整除)（含验算）</v>
       </c>
       <c r="B91" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317308027.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320026565_ll24w.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>544 ÷ 8 (整除)</v>
+        <v>150 ÷ 6 (整除)</v>
       </c>
       <c r="B92" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317310271.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320028054_5ebg3.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>197 ÷ 4 (整除)</v>
+        <v>430 ÷ 6 (整除)</v>
       </c>
       <c r="B93" t="str">
-        <v>❌ 渲染失败 [197÷4(整除)]: Upload failed (409): {"message":"is at 8433281f27515893cafbf967555ab2d4e484ac20 but expected b901e608a5c7576571bd94f364d11e77199d6d55","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>❌ 渲染失败 [430÷6(整除)]: Upload failed (409): {"message":"is at 636655517960dbcab3431d960d997bf3b6af5cf8 but expected d98085b09cdb5b7284fd3055bd65989528bae116","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>208 ÷ 8 (整除)</v>
+        <v>63 ÷ 9 (整除)</v>
       </c>
       <c r="B94" t="str">
-        <v>❌ 渲染失败 [208÷8(整除)]: Upload failed (409): {"message":"is at 8433281f27515893cafbf967555ab2d4e484ac20 but expected b901e608a5c7576571bd94f364d11e77199d6d55","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320027947_54xyi.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>85 ÷ 2 (整除)</v>
+        <v>359 ÷ 5 (整除)</v>
       </c>
       <c r="B95" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317311919.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [359÷5(整除)]: Upload failed (409): {"message":"is at aaf736ef7709610704a4056a56a586ce135ab29e but expected 0064a59b3f724823e061b88654bd5631f47ab2b4","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>301 ÷ 7 (整除)</v>
+        <v>356 ÷ 4 (整除)</v>
       </c>
       <c r="B96" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317311467.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [356÷4(整除)]: Upload failed (409): {"message":"is at aaf736ef7709610704a4056a56a586ce135ab29e but expected 0064a59b3f724823e061b88654bd5631f47ab2b4","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>506 ÷ 6 (整除)（含验算）</v>
+        <v>253 ÷ 5 (整除)（含验算）</v>
       </c>
       <c r="B97" t="str">
-        <v>❌ 渲染失败 [506÷6(整除)]: Upload failed (409): {"message":"is at fe800e91535e88b954f43812a129dfb7710cf689 but expected 3f9558db6572b8b81415a2036a91937a23a60ea9","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320029384_j3166.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>198 ÷ 3 (整除)（含验算）</v>
+        <v>156 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B98" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317313202.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320031348_6tfwm.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>163 ÷ 3 (整除)（含验算）</v>
+        <v>147 ÷ 5 (整除)（含验算）</v>
       </c>
       <c r="B99" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317313541.svg width=120px&gt;&lt;br&gt;</v>
+        <v>❌ 渲染失败 [147÷5(整除)]: Upload failed (409): {"message":"is at 7929b4339c29844f9588b2af72b4e34999f94c57 but expected aaf736ef7709610704a4056a56a586ce135ab29e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>224 ÷ 8 (整除)（含验算）</v>
+        <v>360 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B100" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317312982.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320030958_be9jw.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>158 ÷ 5 (整除)（含验算）</v>
+        <v>350 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B101" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776317315234.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320032839_rj4qx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
   </sheetData>

--- a/eval_results_v2.xlsx
+++ b/eval_results_v2.xlsx
@@ -413,802 +413,802 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>467 + 24</v>
+        <v>741 + 201</v>
       </c>
       <c r="B2" t="str">
-        <v>❌ 渲染失败 [467+24]: Upload failed (409): {"message":"is at 01d9e95f50bb83ce262203cd69464f35c5e70765 but expected 713d48b331519a2492f44a0d22020b67f2d781f0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322125145_icque8.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>520 + 331</v>
+        <v>59 + 38</v>
       </c>
       <c r="B3" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319972780_prgwk.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322126343_tn027t.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>553 + 34</v>
+        <v>444 + 893</v>
       </c>
       <c r="B4" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319969778_zzuwd.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322128588_h2x5bi.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>276 + 426</v>
+        <v>966 + 632</v>
       </c>
       <c r="B5" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319973747_z7t69.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322130841_2kmt61.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>231 + 121</v>
+        <v>960 + 818</v>
       </c>
       <c r="B6" t="str">
-        <v>❌ 渲染失败 [231+121]: Upload failed (409): {"message":"is at 047e818b175243205e5ec92530dd375e138c19da but expected 8a6c5a4c0b48b5350f23e5c2864fbfb02fc83557","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322129824_e529o9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>299 + 690（含验算）</v>
+        <v>641 + 785（含验算）</v>
       </c>
       <c r="B7" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319974013_na04b.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322130051_7ofvuf.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>83 + 245（含验算）</v>
+        <v>772 + 507（含验算）</v>
       </c>
       <c r="B8" t="str">
-        <v>❌ 渲染失败 [83+245]: Upload failed (409): {"message":"is at 4d3bcf996e3be3582d17cf08e07da3894b239631 but expected 047e818b175243205e5ec92530dd375e138c19da","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322132295_b9mjgg.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>143 + 734（含验算）</v>
+        <v>611 + 13（含验算）</v>
       </c>
       <c r="B9" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319975554_9v3r6.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322131993_37m2kz.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>155 + 524（含验算）</v>
+        <v>485 + 492（含验算）</v>
       </c>
       <c r="B10" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319975912_vgz3m.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322133022_6acrou.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>582 + 56（含验算）</v>
+        <v>335 + 44（含验算）</v>
       </c>
       <c r="B11" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319977313_n49ng.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322134068_k78i6b.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>456.7 + 23.9</v>
+        <v>4.1 + 496</v>
       </c>
       <c r="B12" t="str">
-        <v>❌ 渲染失败 [456.7+23.9]: Upload failed (409): {"message":"is at 2029bbb8707d498562677bdd1825284026768208 but expected 2f51808f52d56b45447b6b24021206aa645c9075","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322135990_xi4n37.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>587.09 + 720.23</v>
+        <v>328.92 + 816.46</v>
       </c>
       <c r="B13" t="str">
-        <v>❌ 渲染失败 [587.09+720.23]: Upload failed (409): {"message":"is at 2029bbb8707d498562677bdd1825284026768208 but expected 2f51808f52d56b45447b6b24021206aa645c9075","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322135011_478yjt.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>427.5 + 676.2</v>
+        <v>70.3 + 735.4</v>
       </c>
       <c r="B14" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319980926_n18cb.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322138808_m2nsco.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>146.9 + 959.21</v>
+        <v>357.62 + 341.03</v>
       </c>
       <c r="B15" t="str">
-        <v>❌ 渲染失败 [146.9+959.21]: Upload failed (409): {"message":"is at 9ef9b444c62e4f5f48761a062087c7f211b58799 but expected 2029bbb8707d498562677bdd1825284026768208","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322137826_jrj1u2.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>146.3 + 716.6</v>
+        <v>458.1 + 745.7</v>
       </c>
       <c r="B16" t="str">
-        <v>❌ 渲染失败 [146.3+716.6]: Upload failed (409): {"message":"is at 9ef9b444c62e4f5f48761a062087c7f211b58799 but expected 2029bbb8707d498562677bdd1825284026768208","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322136934_fhesre.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>665.65 + 5.11（含验算）</v>
+        <v>360.17 + 879.95（含验算）</v>
       </c>
       <c r="B17" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319982429_4gpx9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322140340_c65wa6.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>47.8 + 705.4（含验算）</v>
+        <v>898.4 + 227.1（含验算）</v>
       </c>
       <c r="B18" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319982718_zbgq9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322140001_2xo10t.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>843.13 + 272.92（含验算）</v>
+        <v>438.77 + 485.09（含验算）</v>
       </c>
       <c r="B19" t="str">
-        <v>❌ 渲染失败 [843.13+272.92]: Upload failed (409): {"message":"is at d34908ed49ca4cfb65db3488f3948f66896a5fa8 but expected 9ef9b444c62e4f5f48761a062087c7f211b58799","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322141099_jx58rp.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>598.8 + 445.6（含验算）</v>
+        <v>881.8 + 798.4（含验算）</v>
       </c>
       <c r="B20" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319985246_utuuf.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322144262_16sm88.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>651.93 + 764.07（含验算）</v>
+        <v>158.46 + 520.64（含验算）</v>
       </c>
       <c r="B21" t="str">
-        <v>❌ 渲染失败 [651.93+764.07]: Upload failed (409): {"message":"is at f1347171ffde8e60c267f96908edcfa12a6b0961 but expected 26149f418e999921dc627a594dcc0af50b359182","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322142319_gj0gf6.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>95 - 81</v>
+        <v>656 - 526</v>
       </c>
       <c r="B22" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319984956_laqws.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322143345_q3x3o4.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>14 - 7</v>
+        <v>595 - 293</v>
       </c>
       <c r="B23" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319986508_x7cy9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322145211_hwlwmf.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>82 - 59</v>
+        <v>865 - 23</v>
       </c>
       <c r="B24" t="str">
-        <v>❌ 渲染失败 [82-59]: Upload failed (409): {"message":"is at e0feef20aec436755752dcbfc76b78f6b21c555b but expected f333bcc16474956805bd4f8251d8673e5b600523","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322146131_1htef9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>368 - 152</v>
+        <v>764 - 388</v>
       </c>
       <c r="B25" t="str">
-        <v>❌ 渲染失败 [368-152]: Upload failed (409): {"message":"is at e0feef20aec436755752dcbfc76b78f6b21c555b but expected f333bcc16474956805bd4f8251d8673e5b600523","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322146995_mgw0h8.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>342 - 287</v>
+        <v>663 - 347</v>
       </c>
       <c r="B26" t="str">
-        <v>❌ 渲染失败 [342-287]: Upload failed (409): {"message":"is at ba3bf644244c3b6cebd857f1ea2b1f9def9baab0 but expected e0feef20aec436755752dcbfc76b78f6b21c555b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322150539_gi52yv.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>937 - 671（含验算）</v>
+        <v>745 - 270（含验算）</v>
       </c>
       <c r="B27" t="str">
-        <v>❌ 渲染失败 [937-671]: Upload failed (409): {"message":"is at ba3bf644244c3b6cebd857f1ea2b1f9def9baab0 but expected e0feef20aec436755752dcbfc76b78f6b21c555b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322149540_99v29w.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>775 - 101（含验算）</v>
+        <v>73 - 4（含验算）</v>
       </c>
       <c r="B28" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319988049_3fhm3.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322151232_44qkdh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>928 - 265（含验算）</v>
+        <v>607 - 416（含验算）</v>
       </c>
       <c r="B29" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319991347_ht5u7.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322157524_1bss68.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>169 - 109（含验算）</v>
+        <v>947 - 383（含验算）</v>
       </c>
       <c r="B30" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319991646_u2u8b.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322157166_ld533l.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>612 - 483（含验算）</v>
+        <v>170 - 8（含验算）</v>
       </c>
       <c r="B31" t="str">
-        <v>❌ 渲染失败 [612-483]: Upload failed (409): {"message":"is at f68bb8ea3ea3872c95080fe26ed7fea9995cf4e3 but expected ba3bf644244c3b6cebd857f1ea2b1f9def9baab0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322158215_h20can.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>913.3 - 218.6</v>
+        <v>345.9 - 277.1</v>
       </c>
       <c r="B32" t="str">
-        <v>❌ 渲染失败 [913.3-218.6]: Upload failed (409): {"message":"is at 9c5a04ef35b68487ceba8bb1b895e6a0376782ee but expected 4b78fa25c0880e7e80be8c2eed9e3bce34833c61","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322160294_7gw88b.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>562.37 - 141.01</v>
+        <v>469.34 - 221.86</v>
       </c>
       <c r="B33" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319992844_g71by.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322159398_46t067.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>578.1 - 48.8</v>
+        <v>292.4 - 33.2</v>
       </c>
       <c r="B34" t="str">
-        <v>❌ 渲染失败 [578.1-48.8]: Upload failed (409): {"message":"is at 9c5a04ef35b68487ceba8bb1b895e6a0376782ee but expected 4b78fa25c0880e7e80be8c2eed9e3bce34833c61","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322159167_ttdk42.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>942.28 - 821.96</v>
+        <v>51.69 - 18.52</v>
       </c>
       <c r="B35" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319994150_wsghk.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322161254_iy88bx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>123.3 - 69.1</v>
+        <v>764.7 - 567.2</v>
       </c>
       <c r="B36" t="str">
-        <v>❌ 渲染失败 [123.3-69.1]: Upload failed (409): {"message":"is at 7cbf67ec13cc9cf057d44631e4de29059a33d19f but expected 9c5a04ef35b68487ceba8bb1b895e6a0376782ee","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322162067_r5bqw2.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>329.19 - 32.16（含验算）</v>
+        <v>17.98 - 1.94（含验算）</v>
       </c>
       <c r="B37" t="str">
-        <v>❌ 渲染失败 [329.19-32.16]: Upload failed (409): {"message":"is at 7cbf67ec13cc9cf057d44631e4de29059a33d19f but expected 9c5a04ef35b68487ceba8bb1b895e6a0376782ee","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322163092_wqzltq.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>308.3 - 90.3（含验算）</v>
+        <v>877.1 - 487.1（含验算）</v>
       </c>
       <c r="B38" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319995536_8bglr.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322166697_j84w75.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>378.97 - 328.42（含验算）</v>
+        <v>665.44 - 456.03（含验算）</v>
       </c>
       <c r="B39" t="str">
-        <v>❌ 渲染失败 [378.97-328.42]: Upload failed (409): {"message":"is at 9130d1928488235f60ca790799fb040517fc66a0 but expected 7cbf67ec13cc9cf057d44631e4de29059a33d19f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322166972_i9k64w.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>995.9 - 830.1（含验算）</v>
+        <v>438.2 - 182.2（含验算）</v>
       </c>
       <c r="B40" t="str">
-        <v>❌ 渲染失败 [995.9-830.1]: Upload failed (409): {"message":"is at 9130d1928488235f60ca790799fb040517fc66a0 but expected 7cbf67ec13cc9cf057d44631e4de29059a33d19f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322165276_fv2bj0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>387.4 - 11.63（含验算）</v>
+        <v>506.21 - 195.9（含验算）</v>
       </c>
       <c r="B41" t="str">
-        <v>❌ 渲染失败 [387.4-11.63]: Upload failed (409): {"message":"is at 883ca3651c9a68aa4edf142a4aca0924ca286e27 but expected 9130d1928488235f60ca790799fb040517fc66a0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322168346_4wfo4u.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>43 × 4</v>
+        <v>14 × 1</v>
       </c>
       <c r="B42" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319997148_zbwxd.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322169966_wjew4g.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>37 × 9</v>
+        <v>39 × 5</v>
       </c>
       <c r="B43" t="str">
-        <v>❌ 渲染失败 [37×9]: Upload failed (409): {"message":"is at 883ca3651c9a68aa4edf142a4aca0924ca286e27 but expected 9130d1928488235f60ca790799fb040517fc66a0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322169219_9u99mh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>61 × 8</v>
+        <v>6 × 2</v>
       </c>
       <c r="B44" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776319998731_vypd2.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322170907_cc8q5n.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>79 × 2</v>
+        <v>33 × 4</v>
       </c>
       <c r="B45" t="str">
-        <v>❌ 渲染失败 [79×2]: Upload failed (409): {"message":"is at 399b21a0a8449b047393c67fc449a7436c0ae45a but expected 883ca3651c9a68aa4edf142a4aca0924ca286e27","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322171719_4y9kp9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>61 × 4</v>
+        <v>12 × 9</v>
       </c>
       <c r="B46" t="str">
-        <v>❌ 渲染失败 [61×4]: Upload failed (409): {"message":"is at 399b21a0a8449b047393c67fc449a7436c0ae45a but expected 883ca3651c9a68aa4edf142a4aca0924ca286e27","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322171161_sp92cd.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>91 × 9（含验算）</v>
+        <v>97 × 5（含验算）</v>
       </c>
       <c r="B47" t="str">
-        <v>❌ 渲染失败 [91×9]: Upload failed (409): {"message":"is at 29717d2e355c9e399812b60f85c87e8814abfa65 but expected 399b21a0a8449b047393c67fc449a7436c0ae45a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322173933_csk13h.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>70 × 4（含验算）</v>
+        <v>89 × 5（含验算）</v>
       </c>
       <c r="B48" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320000559_0zkrn.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322172726_gtp8zq.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>36 × 3（含验算）</v>
+        <v>88 × 7（含验算）</v>
       </c>
       <c r="B49" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320000853_islpu.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322173193_s78yth.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>33 × 4（含验算）</v>
+        <v>59 × 8（含验算）</v>
       </c>
       <c r="B50" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320002536_yxrof.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322176500_9y6wex.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>64 × 4（含验算）</v>
+        <v>76 × 1（含验算）</v>
       </c>
       <c r="B51" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320002318_c3ru9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322175375_2760v4.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>86 × 1.8</v>
+        <v>88.1 × 2.3</v>
       </c>
       <c r="B52" t="str">
-        <v>❌ 渲染失败 [86×1.8]: Upload failed (409): {"message":"is at 5a3313bccb57951d1239b575d017214ea4dc1b85 but expected cd7f4f8df27585b80b682219a702092c89e20ca3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322175748_zvvceb.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>69 × 6.2</v>
+        <v>57.6 × 2.5</v>
       </c>
       <c r="B53" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320004987_lmprd.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322179717_mk8pj7.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>73.2 × 6.9</v>
+        <v>39.9 × 2.6</v>
       </c>
       <c r="B54" t="str">
-        <v>❌ 渲染失败 [73.2×6.9]: Upload failed (409): {"message":"is at b113cc0cbb0e1055ca1ea95ffdb564e1fdf0fe7f but expected 208efd60594a9cabe0fdfd7c02c492de38c41116","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322180390_xkeazu.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>88.8 × 2.6</v>
+        <v>83.8 × 2.5</v>
       </c>
       <c r="B55" t="str">
-        <v>❌ 渲染失败 [88.8×2.6]: Upload failed (409): {"message":"is at b113cc0cbb0e1055ca1ea95ffdb564e1fdf0fe7f but expected 208efd60594a9cabe0fdfd7c02c492de38c41116","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322179419_23yd74.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>7.9 × 4.2</v>
+        <v>1.6 × 1.9</v>
       </c>
       <c r="B56" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320006108_myhee.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322181369_6d2mzh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>58.2 × 6（含验算）</v>
+        <v>83.8 × 8.4（含验算）</v>
       </c>
       <c r="B57" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320006371_pgv0q.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322182757_5ps49f.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>97.4 × 3.8（含验算）</v>
+        <v>2.6 × 3.6（含验算）</v>
       </c>
       <c r="B58" t="str">
-        <v>❌ 渲染失败 [97.4×3.8]: Upload failed (409): {"message":"is at be6015111a40640004d56157626b7104b4fb00a0 but expected 6b93b68bb9cca91a7b289b47883fe3cafcc337ba","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322181610_1wuk76.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>36.3 × 6.5（含验算）</v>
+        <v>47.1 × 4.1（含验算）</v>
       </c>
       <c r="B59" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320007871_tapq5.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322183953_x0g9jh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>78.3 × 7.8（含验算）</v>
+        <v>64.9 × 8.5（含验算）</v>
       </c>
       <c r="B60" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320008179_4kcue.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322184191_ie1c63.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>14.9 × 6.8（含验算）</v>
+        <v>69.7 × 6.7（含验算）</v>
       </c>
       <c r="B61" t="str">
-        <v>❌ 渲染失败 [14.9×6.8]: Upload failed (409): {"message":"is at 57c3cf0e28e67f88a915ebddc2fdd7d91e6e6b33 but expected be6015111a40640004d56157626b7104b4fb00a0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322185173_m5gsaf.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>30 ÷ 7</v>
+        <v>13 ÷ 3</v>
       </c>
       <c r="B62" t="str">
-        <v>❌ 渲染失败 [30÷7]: Upload failed (409): {"message":"is at a4179a6564e9ca53da43b6ff45abea5b41fdbe13 but expected 93538a39adc33646990ad398dc2b857bee5b409b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322186170_p2vys9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>33 ÷ 8</v>
+        <v>61 ÷ 9</v>
       </c>
       <c r="B63" t="str">
-        <v>❌ 渲染失败 [33÷8]: Upload failed (409): {"message":"is at a4179a6564e9ca53da43b6ff45abea5b41fdbe13 but expected 93538a39adc33646990ad398dc2b857bee5b409b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322186418_60k5tx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>22 ÷ 8</v>
+        <v>76 ÷ 3</v>
       </c>
       <c r="B64" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320010261_apgo4.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322187221_30crro.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>17 ÷ 7</v>
+        <v>95 ÷ 6</v>
       </c>
       <c r="B65" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320012085_tnk9h.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322189611_2zn9mn.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>27 ÷ 8</v>
+        <v>32 ÷ 8</v>
       </c>
       <c r="B66" t="str">
-        <v>❌ 渲染失败 [27÷8]: Upload failed (409): {"message":"is at ace6e6c1dce608c9058f7771e7946b1aab4eadd3 but expected a4179a6564e9ca53da43b6ff45abea5b41fdbe13","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322188475_0e6v3f.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>30 ÷ 7（含验算）</v>
+        <v>93 ÷ 6（含验算）</v>
       </c>
       <c r="B67" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320011932_u9mn2.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322188703_9bk3yn.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>28 ÷ 8（含验算）</v>
+        <v>88 ÷ 4（含验算）</v>
       </c>
       <c r="B68" t="str">
-        <v>❌ 渲染失败 [28÷8]: Upload failed (409): {"message":"is at ddc02e192b654076d9ad05ace73c5bf839a386b7 but expected cb8558f3910b6ff8cf3fdfe2b66666fcede7d7f6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322190853_u5um52.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>85 ÷ 8（含验算）</v>
+        <v>95 ÷ 6（含验算）</v>
       </c>
       <c r="B69" t="str">
-        <v>❌ 渲染失败 [85÷8]: Upload failed (409): {"message":"is at ddc02e192b654076d9ad05ace73c5bf839a386b7 but expected cb8558f3910b6ff8cf3fdfe2b66666fcede7d7f6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322191120_chglif.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>81 ÷ 5（含验算）</v>
+        <v>98 ÷ 6（含验算）</v>
       </c>
       <c r="B70" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320013591_eygax.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322192267_6hyzzs.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>27 ÷ 9（含验算）</v>
+        <v>48 ÷ 6（含验算）</v>
       </c>
       <c r="B71" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320015605_kam80.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322193756_7zhidi.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>58.4 ÷ 4.8</v>
+        <v>90.5 ÷ 6.7</v>
       </c>
       <c r="B72" t="str">
-        <v>❌ 渲染失败 [58.4÷4.8]: Upload failed (409): {"message":"is at d8a60d3599b5924687a5761cb7c93dfa4069d8bc but expected ddc02e192b654076d9ad05ace73c5bf839a386b7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322194059_q0kklt.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>76.6 ÷ 4.5</v>
+        <v>27.2 ÷ 5.2</v>
       </c>
       <c r="B73" t="str">
-        <v>❌ 渲染失败 [76.6÷4.5]: Upload failed (409): {"message":"is at d8a60d3599b5924687a5761cb7c93dfa4069d8bc but expected ddc02e192b654076d9ad05ace73c5bf839a386b7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322194651_ocogl1.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>93.2 ÷ 7.5</v>
+        <v>19.9 ÷ 7.8</v>
       </c>
       <c r="B74" t="str">
-        <v>❌ 渲染失败 [93.2÷7.5]: Upload failed (409): {"message":"is at fa81a2c25e2424544e5c582ad87b4b6bcb613d1a but expected d8a60d3599b5924687a5761cb7c93dfa4069d8bc","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322195948_anlvlp.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>85.3 ÷ 2.2</v>
+        <v>16.3 ÷ 3.4</v>
       </c>
       <c r="B75" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320017450_2u4ri.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322195659_zc8nhn.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>87.5 ÷ 6</v>
+        <v>72.2 ÷ 5.2</v>
       </c>
       <c r="B76" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320017692_25lyt.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322196666_r28dfu.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>51.2 ÷ 6.8（含验算）</v>
+        <v>19.4 ÷ 7.5（含验算）</v>
       </c>
       <c r="B77" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320019221_8gzj0.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322198608_rd46gc.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>15.4 ÷ 6.8（含验算）</v>
+        <v>21.4 ÷ 7.3（含验算）</v>
       </c>
       <c r="B78" t="str">
-        <v>❌ 渲染失败 [15.4÷6.8]: Upload failed (409): {"message":"is at 54e43afff8ebcccaa503d04f98d1aafc4f9928f2 but expected 99dfa6849b6acbfd864c577fe057e9f8f11b544d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322200074_nnzld4.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>59 ÷ 8（含验算）</v>
+        <v>96.4 ÷ 6.1（含验算）</v>
       </c>
       <c r="B79" t="str">
-        <v>❌ 渲染失败 [59÷8]: Upload failed (409): {"message":"is at 54e43afff8ebcccaa503d04f98d1aafc4f9928f2 but expected 99dfa6849b6acbfd864c577fe057e9f8f11b544d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322198998_tcizpx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>31.9 ÷ 8.6（含验算）</v>
+        <v>28.2 ÷ 6.2（含验算）</v>
       </c>
       <c r="B80" t="str">
-        <v>❌ 渲染失败 [31.9÷8.6]: Upload failed (409): {"message":"is at 5c7fa58d66a0cdadbc2644b21d9106afc9269fb3 but expected 04aaf0c0643e930f400233dd15f12d79da04bf40","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322201478_6fb6ns.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>23.8 ÷ 6.1（含验算）</v>
+        <v>25.5 ÷ 6.1（含验算）</v>
       </c>
       <c r="B81" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320021498_so46c.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322202066_yefa3l.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>366 ÷ 6 (整除)</v>
+        <v>138 ÷ 6 (整除)</v>
       </c>
       <c r="B82" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320021232_nerb0.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322203178_tlir5p.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>53 ÷ 2 (整除)</v>
+        <v>23 ÷ 2 (整除)</v>
       </c>
       <c r="B83" t="str">
-        <v>❌ 渲染失败 [53÷2(整除)]: Upload failed (409): {"message":"is at 49ebb53844cfec8a61cb3906d98899bf7eb01373 but expected 5c7fa58d66a0cdadbc2644b21d9106afc9269fb3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322205124_iy1dyc.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>426 ÷ 6 (整除)</v>
+        <v>310 ÷ 5 (整除)</v>
       </c>
       <c r="B84" t="str">
-        <v>❌ 渲染失败 [426÷6(整除)]: Upload failed (409): {"message":"is at 49ebb53844cfec8a61cb3906d98899bf7eb01373 but expected 5c7fa58d66a0cdadbc2644b21d9106afc9269fb3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322204178_1nrwhw.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>297 ÷ 4 (整除)</v>
+        <v>188 ÷ 8 (整除)</v>
       </c>
       <c r="B85" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320023165_wlecr.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322206166_qiod5r.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>612 ÷ 9 (整除)</v>
+        <v>388 ÷ 4 (整除)</v>
       </c>
       <c r="B86" t="str">
-        <v>❌ 渲染失败 [612÷9(整除)]: Upload failed (409): {"message":"is at 2c7a933b4064185cf6f6f644c765874141ffb610 but expected 49ebb53844cfec8a61cb3906d98899bf7eb01373","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322208631_s9vtnz.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>118 ÷ 8 (整除)（含验算）</v>
+        <v>279 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B87" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320024881_6soaz.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322209283_modsk4.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>172 ÷ 2 (整除)（含验算）</v>
+        <v>388 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B88" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320024542_4gqss.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322208146_cv5v8c.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>271 ÷ 8 (整除)（含验算）</v>
+        <v>84 ÷ 5 (整除)（含验算）</v>
       </c>
       <c r="B89" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320026333_xa3ey.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322211699_nwm2ss.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>686 ÷ 7 (整除)（含验算）</v>
+        <v>150 ÷ 2 (整除)（含验算）</v>
       </c>
       <c r="B90" t="str">
-        <v>❌ 渲染失败 [686÷7(整除)]: Upload failed (409): {"message":"is at d98085b09cdb5b7284fd3055bd65989528bae116 but expected 209cf934640c19226ef1ab1f2ed014de0fd53298","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322211001_n9aqcx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>221 ÷ 9 (整除)（含验算）</v>
+        <v>396 ÷ 5 (整除)（含验算）</v>
       </c>
       <c r="B91" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320026565_ll24w.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322211363_3r9p5f.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>150 ÷ 6 (整除)</v>
+        <v>96 ÷ 6 (整除)</v>
       </c>
       <c r="B92" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320028054_5ebg3.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322215287_il0vkh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>430 ÷ 6 (整除)</v>
+        <v>111 ÷ 6 (整除)</v>
       </c>
       <c r="B93" t="str">
-        <v>❌ 渲染失败 [430÷6(整除)]: Upload failed (409): {"message":"is at 636655517960dbcab3431d960d997bf3b6af5cf8 but expected d98085b09cdb5b7284fd3055bd65989528bae116","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322214290_6y3shk.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>63 ÷ 9 (整除)</v>
+        <v>384 ÷ 4 (整除)</v>
       </c>
       <c r="B94" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320027947_54xyi.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322217519_jz8y2u.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>359 ÷ 5 (整除)</v>
+        <v>247 ÷ 3 (整除)</v>
       </c>
       <c r="B95" t="str">
-        <v>❌ 渲染失败 [359÷5(整除)]: Upload failed (409): {"message":"is at aaf736ef7709610704a4056a56a586ce135ab29e but expected 0064a59b3f724823e061b88654bd5631f47ab2b4","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322219260_15xb2q.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>356 ÷ 4 (整除)</v>
+        <v>414 ÷ 9 (整除)</v>
       </c>
       <c r="B96" t="str">
-        <v>❌ 渲染失败 [356÷4(整除)]: Upload failed (409): {"message":"is at aaf736ef7709610704a4056a56a586ce135ab29e but expected 0064a59b3f724823e061b88654bd5631f47ab2b4","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322220200_rjcacp.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>253 ÷ 5 (整除)（含验算）</v>
+        <v>95 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B97" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320029384_j3166.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322218994_qak4r0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>156 ÷ 4 (整除)（含验算）</v>
+        <v>210 ÷ 6 (整除)（含验算）</v>
       </c>
       <c r="B98" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320031348_6tfwm.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322221693_wvikiz.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>147 ÷ 5 (整除)（含验算）</v>
+        <v>14 ÷ 3 (整除)（含验算）</v>
       </c>
       <c r="B99" t="str">
-        <v>❌ 渲染失败 [147÷5(整除)]: Upload failed (409): {"message":"is at 7929b4339c29844f9588b2af72b4e34999f94c57 but expected aaf736ef7709610704a4056a56a586ce135ab29e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322223129_3970l9.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>360 ÷ 4 (整除)（含验算）</v>
+        <v>162 ÷ 6 (整除)（含验算）</v>
       </c>
       <c r="B100" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320030958_be9jw.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322221405_ktt1lr.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>350 ÷ 4 (整除)（含验算）</v>
+        <v>13 ÷ 2 (整除)（含验算）</v>
       </c>
       <c r="B101" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776320032839_rj4qx.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322224706_ar6vph.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
   </sheetData>

--- a/eval_results_v2.xlsx
+++ b/eval_results_v2.xlsx
@@ -413,802 +413,802 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>741 + 201</v>
+        <v>304 + 628</v>
       </c>
       <c r="B2" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322125145_icque8.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776328948521_odhf27.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>59 + 38</v>
+        <v>534 + 960</v>
       </c>
       <c r="B3" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322126343_tn027t.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776328947315_awm9bq.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>444 + 893</v>
+        <v>919 + 691</v>
       </c>
       <c r="B4" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322128588_h2x5bi.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329010194_dwggfm.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>966 + 632</v>
+        <v>557 + 359</v>
       </c>
       <c r="B5" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322130841_2kmt61.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329011721_hdsfvi.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>960 + 818</v>
+        <v>886 + 314</v>
       </c>
       <c r="B6" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322129824_e529o9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329012593_xpxt1i.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>641 + 785（含验算）</v>
+        <v>87 + 213（含验算）</v>
       </c>
       <c r="B7" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322130051_7ofvuf.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329013361_ncyyws.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>772 + 507（含验算）</v>
+        <v>113 + 50（含验算）</v>
       </c>
       <c r="B8" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322132295_b9mjgg.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329014751_7lcvxt.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>611 + 13（含验算）</v>
+        <v>245 + 777（含验算）</v>
       </c>
       <c r="B9" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322131993_37m2kz.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329014478_s86l31.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>485 + 492（含验算）</v>
+        <v>607 + 554（含验算）</v>
       </c>
       <c r="B10" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322133022_6acrou.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329015815_decvqd.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>335 + 44（含验算）</v>
+        <v>227 + 201（含验算）</v>
       </c>
       <c r="B11" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322134068_k78i6b.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329019549_f0kbsc.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>4.1 + 496</v>
+        <v>475.5 + 951.3</v>
       </c>
       <c r="B12" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322135990_xi4n37.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329017627_faxcbt.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>328.92 + 816.46</v>
+        <v>271.33 + 306.14</v>
       </c>
       <c r="B13" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322135011_478yjt.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329018563_jrgcbk.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>70.3 + 735.4</v>
+        <v>996.9 + 246.9</v>
       </c>
       <c r="B14" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322138808_m2nsco.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329022651_cvuwsc.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>357.62 + 341.03</v>
+        <v>45.95 + 280.61</v>
       </c>
       <c r="B15" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322137826_jrj1u2.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329020633_3g3uat.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>458.1 + 745.7</v>
+        <v>893.8 + 278.2</v>
       </c>
       <c r="B16" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322136934_fhesre.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329021648_flkinm.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>360.17 + 879.95（含验算）</v>
+        <v>878.4 + 884.33（含验算）</v>
       </c>
       <c r="B17" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322140340_c65wa6.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329024132_ob7c2j.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>898.4 + 227.1（含验算）</v>
+        <v>637.9 + 325.5（含验算）</v>
       </c>
       <c r="B18" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322140001_2xo10t.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329024454_76eu6u.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>438.77 + 485.09（含验算）</v>
+        <v>244.13 + 212.11（含验算）</v>
       </c>
       <c r="B19" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322141099_jx58rp.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329025143_003fym.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>881.8 + 798.4（含验算）</v>
+        <v>888.3 + 206.1（含验算）</v>
       </c>
       <c r="B20" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322144262_16sm88.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329026247_4gywbx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>158.46 + 520.64（含验算）</v>
+        <v>727.32 + 796.75（含验算）</v>
       </c>
       <c r="B21" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322142319_gj0gf6.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329028360_47ljjt.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>656 - 526</v>
+        <v>890 - 342</v>
       </c>
       <c r="B22" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322143345_q3x3o4.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329027257_04onii.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>595 - 293</v>
+        <v>605 - 149</v>
       </c>
       <c r="B23" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322145211_hwlwmf.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329029397_x2i2fc.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>865 - 23</v>
+        <v>21 - 16</v>
       </c>
       <c r="B24" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322146131_1htef9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329030448_6ys96z.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>764 - 388</v>
+        <v>208 - 148</v>
       </c>
       <c r="B25" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322146995_mgw0h8.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329031399_fg7vw0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>663 - 347</v>
+        <v>204 - 65</v>
       </c>
       <c r="B26" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322150539_gi52yv.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329032657_9vus7x.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>745 - 270（含验算）</v>
+        <v>849 - 357（含验算）</v>
       </c>
       <c r="B27" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322149540_99v29w.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329033490_827ltx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>73 - 4（含验算）</v>
+        <v>649 - 425（含验算）</v>
       </c>
       <c r="B28" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322151232_44qkdh.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329032415_i1xcch.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>607 - 416（含验算）</v>
+        <v>729 - 386（含验算）</v>
       </c>
       <c r="B29" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322157524_1bss68.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329034851_q7mq42.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>947 - 383（含验算）</v>
+        <v>832 - 420（含验算）</v>
       </c>
       <c r="B30" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322157166_ld533l.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329035122_myomba.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>170 - 8（含验算）</v>
+        <v>423 - 27（含验算）</v>
       </c>
       <c r="B31" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322158215_h20can.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329036349_5ku7gt.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>345.9 - 277.1</v>
+        <v>587.6 - 223.4</v>
       </c>
       <c r="B32" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322160294_7gw88b.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329038521_l1pezn.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>469.34 - 221.86</v>
+        <v>349.23 - 46.58</v>
       </c>
       <c r="B33" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322159398_46t067.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329038751_o09e7u.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>292.4 - 33.2</v>
+        <v>24.8 - 1.3</v>
       </c>
       <c r="B34" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322159167_ttdk42.svg width=120px&gt;&lt;br&gt;</v>
+        <v>ERROR: Parse Error: Invalid character in chunk size</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>51.69 - 18.52</v>
+        <v>540.12 - 162.49</v>
       </c>
       <c r="B35" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322161254_iy88bx.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329040069_b4pw13.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>764.7 - 567.2</v>
+        <v>52.5 - 27.1</v>
       </c>
       <c r="B36" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322162067_r5bqw2.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329040960_ump2ar.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>17.98 - 1.94（含验算）</v>
+        <v>77.99 - 36.34（含验算）</v>
       </c>
       <c r="B37" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322163092_wqzltq.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329042309_1w4t68.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>877.1 - 487.1（含验算）</v>
+        <v>844 - 528.2（含验算）</v>
       </c>
       <c r="B38" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322166697_j84w75.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329043898_4g3han.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>665.44 - 456.03（含验算）</v>
+        <v>25.72 - 2.32（含验算）</v>
       </c>
       <c r="B39" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322166972_i9k64w.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329045259_eqfx8r.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>438.2 - 182.2（含验算）</v>
+        <v>688.2 - 149（含验算）</v>
       </c>
       <c r="B40" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322165276_fv2bj0.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329043465_2ksylz.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>506.21 - 195.9（含验算）</v>
+        <v>789.96 - 566.51（含验算）</v>
       </c>
       <c r="B41" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322168346_4wfo4u.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329048514_c6nsml.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>14 × 1</v>
+        <v>55 × 4</v>
       </c>
       <c r="B42" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322169966_wjew4g.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329046556_sklk3m.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>39 × 5</v>
+        <v>79 × 3</v>
       </c>
       <c r="B43" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322169219_9u99mh.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329047568_t23m2x.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>6 × 2</v>
+        <v>12 × 4</v>
       </c>
       <c r="B44" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322170907_cc8q5n.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329049958_shb051.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>33 × 4</v>
+        <v>51 × 8</v>
       </c>
       <c r="B45" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322171719_4y9kp9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329050780_taxlml.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>12 × 9</v>
+        <v>82 × 6</v>
       </c>
       <c r="B46" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322171161_sp92cd.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329051865_lxx8eh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>97 × 5（含验算）</v>
+        <v>22 × 2（含验算）</v>
       </c>
       <c r="B47" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322173933_csk13h.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329053491_eqsj9z.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>89 × 5（含验算）</v>
+        <v>47 × 5（含验算）</v>
       </c>
       <c r="B48" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322172726_gtp8zq.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329053138_18osim.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>88 × 7（含验算）</v>
+        <v>80 × 2（含验算）</v>
       </c>
       <c r="B49" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322173193_s78yth.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329054362_jg1eqm.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>59 × 8（含验算）</v>
+        <v>89 × 5（含验算）</v>
       </c>
       <c r="B50" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322176500_9y6wex.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329055833_64y57k.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>76 × 1（含验算）</v>
+        <v>27 × 3（含验算）</v>
       </c>
       <c r="B51" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322175375_2760v4.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329056483_syd5n1.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>88.1 × 2.3</v>
+        <v>49.3 × 4.9</v>
       </c>
       <c r="B52" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322175748_zvvceb.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329055428_d7vtp2.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>57.6 × 2.5</v>
+        <v>89.7 × 7.4</v>
       </c>
       <c r="B53" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322179717_mk8pj7.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329059891_5m4pyi.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>39.9 × 2.6</v>
+        <v>37.3 × 1.1</v>
       </c>
       <c r="B54" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322180390_xkeazu.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329060905_198i5k.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>83.8 × 2.5</v>
+        <v>7.7 × 1.5</v>
       </c>
       <c r="B55" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322179419_23yd74.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329058890_nteaqu.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>1.6 × 1.9</v>
+        <v>75.4 × 7.4</v>
       </c>
       <c r="B56" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322181369_6d2mzh.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329065432_1o3fj8.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>83.8 × 8.4（含验算）</v>
+        <v>72.6 × 1.2（含验算）</v>
       </c>
       <c r="B57" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322182757_5ps49f.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329063424_0a59r1.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2.6 × 3.6（含验算）</v>
+        <v>95.1 × 3.2（含验算）</v>
       </c>
       <c r="B58" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322181610_1wuk76.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329064340_zfc8q0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>47.1 × 4.1（含验算）</v>
+        <v>2.3 × 8（含验算）</v>
       </c>
       <c r="B59" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322183953_x0g9jh.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329067685_p2ealv.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>64.9 × 8.5（含验算）</v>
+        <v>86.4 × 1.5（含验算）</v>
       </c>
       <c r="B60" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322184191_ie1c63.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329066579_3rki0m.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>69.7 × 6.7（含验算）</v>
+        <v>58.3 × 5.9（含验算）</v>
       </c>
       <c r="B61" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322185173_m5gsaf.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329068907_g8nnts.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>13 ÷ 3</v>
+        <v>77 ÷ 4</v>
       </c>
       <c r="B62" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322186170_p2vys9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329072011_hckn9h.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>61 ÷ 9</v>
+        <v>24 ÷ 4</v>
       </c>
       <c r="B63" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322186418_60k5tx.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329071169_nmpxze.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>76 ÷ 3</v>
+        <v>75 ÷ 7</v>
       </c>
       <c r="B64" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322187221_30crro.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329070007_evkry0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>95 ÷ 6</v>
+        <v>90 ÷ 4</v>
       </c>
       <c r="B65" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322189611_2zn9mn.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329074488_ewomgj.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>32 ÷ 8</v>
+        <v>65 ÷ 8</v>
       </c>
       <c r="B66" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322188475_0e6v3f.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329074797_sz8mqf.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>93 ÷ 6（含验算）</v>
+        <v>52 ÷ 3（含验算）</v>
       </c>
       <c r="B67" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322188703_9bk3yn.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329073625_k5ol36.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>88 ÷ 4（含验算）</v>
+        <v>82 ÷ 8（含验算）</v>
       </c>
       <c r="B68" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322190853_u5um52.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329079004_d3uajs.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>95 ÷ 6（含验算）</v>
+        <v>35 ÷ 7（含验算）</v>
       </c>
       <c r="B69" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322191120_chglif.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329078717_im1ynv.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>98 ÷ 6（含验算）</v>
+        <v>49 ÷ 5（含验算）</v>
       </c>
       <c r="B70" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322192267_6hyzzs.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329079766_o3n5d3.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>48 ÷ 6（含验算）</v>
+        <v>14 ÷ 2（含验算）</v>
       </c>
       <c r="B71" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322193756_7zhidi.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329081056_lwpqjd.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>90.5 ÷ 6.7</v>
+        <v>95.4 ÷ 3.2</v>
       </c>
       <c r="B72" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322194059_q0kklt.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329081912_cohepu.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>27.2 ÷ 5.2</v>
+        <v>81.8 ÷ 6.9</v>
       </c>
       <c r="B73" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322194651_ocogl1.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329082800_yz6sdh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>19.9 ÷ 7.8</v>
+        <v>45.8 ÷ 2.9</v>
       </c>
       <c r="B74" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322195948_anlvlp.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329084798_cetq9y.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>16.3 ÷ 3.4</v>
+        <v>74.6 ÷ 6.3</v>
       </c>
       <c r="B75" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322195659_zc8nhn.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329085059_sqiufx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>72.2 ÷ 5.2</v>
+        <v>46.7 ÷ 6.6</v>
       </c>
       <c r="B76" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322196666_r28dfu.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329083876_yf8rgd.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>19.4 ÷ 7.5（含验算）</v>
+        <v>61.8 ÷ 5.3（含验算）</v>
       </c>
       <c r="B77" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322198608_rd46gc.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329088780_i9h7kl.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>21.4 ÷ 7.3（含验算）</v>
+        <v>23.9 ÷ 2.7（含验算）</v>
       </c>
       <c r="B78" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322200074_nnzld4.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329087482_mamjmo.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>96.4 ÷ 6.1（含验算）</v>
+        <v>86.7 ÷ 6.8（含验算）</v>
       </c>
       <c r="B79" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322198998_tcizpx.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329087795_tivcl5.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>28.2 ÷ 6.2（含验算）</v>
+        <v>86.5 ÷ 8.5（含验算）</v>
       </c>
       <c r="B80" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322201478_6fb6ns.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329091123_jodvt0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>25.5 ÷ 6.1（含验算）</v>
+        <v>29.8 ÷ 6.6（含验算）</v>
       </c>
       <c r="B81" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322202066_yefa3l.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329090358_70ddri.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>138 ÷ 6 (整除)</v>
+        <v>170 ÷ 5 (整除)</v>
       </c>
       <c r="B82" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322203178_tlir5p.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329090060_1cj579.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>23 ÷ 2 (整除)</v>
+        <v>53 ÷ 5 (整除)</v>
       </c>
       <c r="B83" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322205124_iy1dyc.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329094209_b34rf0.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>310 ÷ 5 (整除)</v>
+        <v>160 ÷ 8 (整除)</v>
       </c>
       <c r="B84" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322204178_1nrwhw.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329093113_hjj0x4.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>188 ÷ 8 (整除)</v>
+        <v>397 ÷ 7 (整除)</v>
       </c>
       <c r="B85" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322206166_qiod5r.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329095190_3sayck.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>388 ÷ 4 (整除)</v>
+        <v>266 ÷ 7 (整除)</v>
       </c>
       <c r="B86" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322208631_s9vtnz.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329096624_xp4v3v.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>279 ÷ 4 (整除)（含验算）</v>
+        <v>281 ÷ 6 (整除)（含验算）</v>
       </c>
       <c r="B87" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322209283_modsk4.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329097906_zqdozz.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>388 ÷ 4 (整除)（含验算）</v>
+        <v>54 ÷ 6 (整除)（含验算）</v>
       </c>
       <c r="B88" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322208146_cv5v8c.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329097008_h91miq.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>84 ÷ 5 (整除)（含验算）</v>
+        <v>28 ÷ 3 (整除)（含验算）</v>
       </c>
       <c r="B89" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322211699_nwm2ss.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329099797_ukec3d.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>150 ÷ 2 (整除)（含验算）</v>
+        <v>630 ÷ 9 (整除)（含验算）</v>
       </c>
       <c r="B90" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322211001_n9aqcx.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329100386_ixpgt6.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>396 ÷ 5 (整除)（含验算）</v>
+        <v>160 ÷ 3 (整除)（含验算）</v>
       </c>
       <c r="B91" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322211363_3r9p5f.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329099143_0u5hpp.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>96 ÷ 6 (整除)</v>
+        <v>372 ÷ 6 (整除)</v>
       </c>
       <c r="B92" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322215287_il0vkh.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329101692_ya3nfu.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>111 ÷ 6 (整除)</v>
+        <v>146 ÷ 4 (整除)</v>
       </c>
       <c r="B93" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322214290_6y3shk.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329102742_k7q23x.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>384 ÷ 4 (整除)</v>
+        <v>30 ÷ 5 (整除)</v>
       </c>
       <c r="B94" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322217519_jz8y2u.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329103675_sgxbuk.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>247 ÷ 3 (整除)</v>
+        <v>484 ÷ 6 (整除)</v>
       </c>
       <c r="B95" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322219260_15xb2q.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329104853_lrpgsk.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>414 ÷ 9 (整除)</v>
+        <v>192 ÷ 6 (整除)</v>
       </c>
       <c r="B96" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322220200_rjcacp.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329105689_8fh7bh.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>95 ÷ 4 (整除)（含验算）</v>
+        <v>163 ÷ 3 (整除)（含验算）</v>
       </c>
       <c r="B97" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322218994_qak4r0.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329105218_thhg1q.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>210 ÷ 6 (整除)（含验算）</v>
+        <v>300 ÷ 6 (整除)（含验算）</v>
       </c>
       <c r="B98" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322221693_wvikiz.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329106838_xx8g1z.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>14 ÷ 3 (整除)（含验算）</v>
+        <v>306 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B99" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322223129_3970l9.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329107975_0toiwx.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>162 ÷ 6 (整除)（含验算）</v>
+        <v>56 ÷ 4 (整除)（含验算）</v>
       </c>
       <c r="B100" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322221405_ktt1lr.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329107236_ny44no.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>13 ÷ 2 (整除)（含验算）</v>
+        <v>435 ÷ 9 (整除)（含验算）</v>
       </c>
       <c r="B101" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776322224706_ar6vph.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776329110047_c5zu3m.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
   </sheetData>
